--- a/data/dividends_info_20261001.xlsx
+++ b/data/dividends_info_20261001.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.17499923706055</v>
+        <v>47.25</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1907790173938069</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="J2" t="n">
         <v>165</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>63.20000076293945</v>
+        <v>62.84999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.107594923338167</v>
+        <v>1.113762954645464</v>
       </c>
       <c r="J3" t="n">
         <v>144</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.760000228881836</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6849314889533816</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>74</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.15499877929688</v>
+        <v>47.25</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1908599349588234</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="J6" t="n">
         <v>74</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.025000095367432</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="I7" t="n">
-        <v>3.802468956725087</v>
+        <v>3.79310350173476</v>
       </c>
       <c r="J7" t="n">
         <v>53</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>49.5</v>
+        <v>49.95999908447266</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6680808080808081</v>
+        <v>0.6619295557649041</v>
       </c>
       <c r="J8" t="n">
         <v>53</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.9950008392334</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="I9" t="n">
-        <v>1.125234384482839</v>
+        <v>1.123595473511786</v>
       </c>
       <c r="J9" t="n">
         <v>53</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>24.21999931335449</v>
+        <v>24.45999908447266</v>
       </c>
       <c r="I10" t="n">
-        <v>2.436003372116877</v>
+        <v>2.412101480308457</v>
       </c>
       <c r="J10" t="n">
         <v>53</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12.07999992370605</v>
+        <v>11.96000003814697</v>
       </c>
       <c r="I11" t="n">
-        <v>1.738410607005812</v>
+        <v>1.755852837208991</v>
       </c>
       <c r="J11" t="n">
         <v>46</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.099999904632568</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I13" t="n">
-        <v>1.147541001547219</v>
+        <v>1.157024756911577</v>
       </c>
       <c r="J13" t="n">
         <v>39</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.659999847412109</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I14" t="n">
-        <v>0.621118022233446</v>
+        <v>0.6493506654355597</v>
       </c>
       <c r="J14" t="n">
         <v>39</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.46000003814697</v>
+        <v>10.47000026702881</v>
       </c>
       <c r="I15" t="n">
-        <v>4.397705528894918</v>
+        <v>4.393505141051342</v>
       </c>
       <c r="J15" t="n">
         <v>25</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.179999828338623</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9652509972386709</v>
+        <v>0.980392175195585</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.800000190734863</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>0.487179475266396</v>
+        <v>0.4960835607958674</v>
       </c>
       <c r="J19" t="n">
         <v>-3</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23.9950008392334</v>
+        <v>24.03000068664551</v>
       </c>
       <c r="I20" t="n">
-        <v>1.125234384482839</v>
+        <v>1.123595473511786</v>
       </c>
       <c r="J20" t="n">
         <v>-10</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.886000037193298</v>
+        <v>1.878999948501587</v>
       </c>
       <c r="I21" t="n">
-        <v>3.022269293526955</v>
+        <v>3.033528555732787</v>
       </c>
       <c r="J21" t="n">
         <v>-10</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>47.15499877929688</v>
+        <v>47.25</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1908599349588234</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="J22" t="n">
         <v>-10</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>92.80000305175781</v>
+        <v>94.55000305175781</v>
       </c>
       <c r="I23" t="n">
-        <v>1.433189608041513</v>
+        <v>1.406663095792754</v>
       </c>
       <c r="J23" t="n">
         <v>-10</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.179999828338623</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I24" t="n">
-        <v>4.854369066878265</v>
+        <v>4.838709826275912</v>
       </c>
       <c r="J24" t="n">
         <v>-17</v>
@@ -3528,214 +3528,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ErreDue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>POWERSOFT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Redelfi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>